--- a/Mumbai-June-2025.xlsx
+++ b/Mumbai-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="146">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Mumbai</t>
   </si>
   <si>
@@ -316,28 +319,28 @@
     <t>MH02GH2432</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>ETIOS</t>
   </si>
   <si>
-    <t>HYRIDER</t>
-  </si>
-  <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>CITRON</t>
-  </si>
-  <si>
-    <t>TATA TIGORE</t>
+    <t>HYRYDER</t>
+  </si>
+  <si>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
+  </si>
+  <si>
+    <t>TATA TIGOR</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>BYD</t>
+    <t>BYD E6</t>
   </si>
   <si>
     <t>CAMRY</t>
@@ -346,13 +349,13 @@
     <t>INVICTO</t>
   </si>
   <si>
-    <t>Hycross</t>
-  </si>
-  <si>
-    <t>Merc E</t>
-  </si>
-  <si>
-    <t>5 Series</t>
+    <t>HYCROSS</t>
+  </si>
+  <si>
+    <t>MERCEDES E</t>
+  </si>
+  <si>
+    <t>5 SERIES</t>
   </si>
   <si>
     <t>URBANIA</t>
@@ -361,13 +364,103 @@
     <t>XUV 400</t>
   </si>
   <si>
-    <t>-</t>
+    <t>24/04/2019</t>
+  </si>
+  <si>
+    <t>16/08/2018</t>
+  </si>
+  <si>
+    <t>30/03/2019</t>
+  </si>
+  <si>
+    <t>26/04/2019</t>
+  </si>
+  <si>
+    <t>31/08/2019</t>
+  </si>
+  <si>
+    <t>18/07/2022</t>
+  </si>
+  <si>
+    <t>18/08/2022</t>
+  </si>
+  <si>
+    <t>21/10/2022</t>
+  </si>
+  <si>
+    <t>30/09/2019</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>27/06/2019</t>
+  </si>
+  <si>
+    <t>16/01/2019</t>
+  </si>
+  <si>
+    <t>21/10/2021</t>
+  </si>
+  <si>
+    <t>31/10/2024</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>21/09/2021</t>
+  </si>
+  <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
+    <t>21/04/2025</t>
+  </si>
+  <si>
+    <t>14/04/2023</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>27/05/2025</t>
+  </si>
+  <si>
+    <t>15/02/2023</t>
+  </si>
+  <si>
+    <t>31/05/2022</t>
+  </si>
+  <si>
+    <t>16/08/2024</t>
+  </si>
+  <si>
+    <t>19/12/2023</t>
+  </si>
+  <si>
+    <t>27/06/2025</t>
+  </si>
+  <si>
+    <t>22/04/2025</t>
+  </si>
+  <si>
+    <t>18/03/2020</t>
+  </si>
+  <si>
+    <t>23/12/2024</t>
+  </si>
+  <si>
+    <t>22/01/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -420,11 +513,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,10 +813,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z73"/>
+  <dimension ref="A1:AA73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,28 +895,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2">
-        <v>43579</v>
+        <v>101</v>
+      </c>
+      <c r="G2" t="s">
+        <v>116</v>
       </c>
       <c r="H2">
         <v>142602</v>
@@ -882,27 +979,27 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3">
-        <v>43579</v>
+        <v>101</v>
+      </c>
+      <c r="G3" t="s">
+        <v>116</v>
       </c>
       <c r="H3">
         <v>140480</v>
@@ -962,27 +1059,27 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>121</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>44470</v>
+        <v>101</v>
+      </c>
+      <c r="G4" s="2">
+        <v>44206</v>
       </c>
       <c r="H4">
         <v>61293</v>
@@ -1042,27 +1139,27 @@
         <v>57.94</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H5">
         <v>109923</v>
@@ -1122,27 +1219,27 @@
         <v>52.28</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6">
-        <v>43554</v>
+        <v>101</v>
+      </c>
+      <c r="G6" t="s">
+        <v>118</v>
       </c>
       <c r="H6">
         <v>231282</v>
@@ -1202,27 +1299,27 @@
         <v>30.76</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>124</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H7">
         <v>255359</v>
@@ -1282,27 +1379,27 @@
         <v>57.74</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>125</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8">
-        <v>43501</v>
+        <v>101</v>
+      </c>
+      <c r="G8" s="2">
+        <v>43587</v>
       </c>
       <c r="H8">
         <v>103927</v>
@@ -1362,27 +1459,27 @@
         <v>54.26</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9">
-        <v>43708</v>
+        <v>101</v>
+      </c>
+      <c r="G9" t="s">
+        <v>120</v>
       </c>
       <c r="H9">
         <v>61603</v>
@@ -1442,27 +1539,27 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10">
-        <v>44663</v>
+        <v>101</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44899</v>
       </c>
       <c r="H10">
         <v>146432</v>
@@ -1522,27 +1619,27 @@
         <v>43.08</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11">
-        <v>44663</v>
+        <v>101</v>
+      </c>
+      <c r="G11" s="2">
+        <v>44899</v>
       </c>
       <c r="H11">
         <v>135278</v>
@@ -1602,27 +1699,27 @@
         <v>59.77</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>129</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12">
-        <v>44663</v>
+        <v>101</v>
+      </c>
+      <c r="G12" s="2">
+        <v>44899</v>
       </c>
       <c r="H12">
         <v>118676</v>
@@ -1682,26 +1779,26 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>130</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13">
+        <v>101</v>
+      </c>
+      <c r="G13" s="2">
         <v>44686</v>
       </c>
       <c r="H13">
@@ -1762,26 +1859,26 @@
         <v>65.92</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14">
+        <v>101</v>
+      </c>
+      <c r="G14" s="2">
         <v>44686</v>
       </c>
       <c r="H14">
@@ -1842,27 +1939,27 @@
         <v>51.55</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>100</v>
-      </c>
-      <c r="G15">
-        <v>44760</v>
+        <v>101</v>
+      </c>
+      <c r="G15" t="s">
+        <v>121</v>
       </c>
       <c r="H15">
         <v>113755</v>
@@ -1922,27 +2019,27 @@
         <v>22.86</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16">
-        <v>44791</v>
+        <v>101</v>
+      </c>
+      <c r="G16" t="s">
+        <v>122</v>
       </c>
       <c r="H16">
         <v>151357</v>
@@ -2007,22 +2104,22 @@
         <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17">
-        <v>44855</v>
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
+        <v>123</v>
       </c>
       <c r="H17">
         <v>72877</v>
@@ -2087,22 +2184,22 @@
         <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18">
-        <v>44236</v>
+        <v>101</v>
+      </c>
+      <c r="G18" s="2">
+        <v>44441</v>
       </c>
       <c r="H18">
         <v>132884</v>
@@ -2167,22 +2264,22 @@
         <v>136</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19">
-        <v>43899</v>
+        <v>101</v>
+      </c>
+      <c r="G19" s="2">
+        <v>44077</v>
       </c>
       <c r="H19">
         <v>104661</v>
@@ -2247,22 +2344,22 @@
         <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20">
-        <v>43738</v>
+        <v>101</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
       </c>
       <c r="H20">
         <v>161639</v>
@@ -2327,22 +2424,22 @@
         <v>138</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21">
-        <v>44280</v>
+        <v>101</v>
+      </c>
+      <c r="G21" t="s">
+        <v>125</v>
       </c>
       <c r="H21">
         <v>78802</v>
@@ -2407,22 +2504,22 @@
         <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22">
-        <v>43738</v>
+        <v>101</v>
+      </c>
+      <c r="G22" t="s">
+        <v>124</v>
       </c>
       <c r="H22">
         <v>154005</v>
@@ -2487,22 +2584,22 @@
         <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23">
-        <v>44236</v>
+        <v>101</v>
+      </c>
+      <c r="G23" s="2">
+        <v>44441</v>
       </c>
       <c r="H23">
         <v>58515</v>
@@ -2567,22 +2664,22 @@
         <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24">
-        <v>43643</v>
+        <v>101</v>
+      </c>
+      <c r="G24" t="s">
+        <v>126</v>
       </c>
       <c r="H24">
         <v>118253</v>
@@ -2647,22 +2744,22 @@
         <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G25">
-        <v>44236</v>
+        <v>101</v>
+      </c>
+      <c r="G25" s="2">
+        <v>44441</v>
       </c>
       <c r="H25">
         <v>103218</v>
@@ -2727,22 +2824,22 @@
         <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26">
-        <v>44237</v>
+        <v>101</v>
+      </c>
+      <c r="G26" s="2">
+        <v>44471</v>
       </c>
       <c r="H26">
         <v>87233</v>
@@ -2807,22 +2904,22 @@
         <v>144</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27">
-        <v>43481</v>
+        <v>101</v>
+      </c>
+      <c r="G27" t="s">
+        <v>127</v>
       </c>
       <c r="H27">
         <v>100297</v>
@@ -2887,22 +2984,22 @@
         <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <v>44470</v>
+        <v>101</v>
+      </c>
+      <c r="G28" s="2">
+        <v>44206</v>
       </c>
       <c r="H28">
         <v>76874</v>
@@ -2967,22 +3064,22 @@
         <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29">
-        <v>44490</v>
+        <v>101</v>
+      </c>
+      <c r="G29" t="s">
+        <v>128</v>
       </c>
       <c r="H29">
         <v>94603</v>
@@ -3047,22 +3144,22 @@
         <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30">
-        <v>43808</v>
+        <v>101</v>
+      </c>
+      <c r="G30" s="2">
+        <v>43720</v>
       </c>
       <c r="H30">
         <v>162990</v>
@@ -3127,22 +3224,22 @@
         <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31">
-        <v>43808</v>
+        <v>101</v>
+      </c>
+      <c r="G31" s="2">
+        <v>43720</v>
       </c>
       <c r="H31">
         <v>153102</v>
@@ -3207,22 +3304,22 @@
         <v>149</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32">
-        <v>45596</v>
+        <v>101</v>
+      </c>
+      <c r="G32" t="s">
+        <v>129</v>
       </c>
       <c r="H32">
         <v>32790</v>
@@ -3287,22 +3384,22 @@
         <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33">
-        <v>45715</v>
+        <v>101</v>
+      </c>
+      <c r="G33" t="s">
+        <v>130</v>
       </c>
       <c r="H33">
         <v>14072</v>
@@ -3367,22 +3464,22 @@
         <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34">
-        <v>45715</v>
+        <v>101</v>
+      </c>
+      <c r="G34" t="s">
+        <v>130</v>
       </c>
       <c r="H34">
         <v>12615</v>
@@ -3447,22 +3544,22 @@
         <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
-      </c>
-      <c r="G35">
-        <v>45715</v>
+        <v>101</v>
+      </c>
+      <c r="G35" t="s">
+        <v>130</v>
       </c>
       <c r="H35">
         <v>11938</v>
@@ -3527,22 +3624,22 @@
         <v>153</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>100</v>
-      </c>
-      <c r="G36" t="s">
-        <v>115</v>
+        <v>101</v>
+      </c>
+      <c r="G36" s="2">
+        <v>43720</v>
       </c>
       <c r="H36">
         <v>50345</v>
@@ -3607,22 +3704,22 @@
         <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>100</v>
-      </c>
-      <c r="G37">
-        <v>44460</v>
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
+        <v>131</v>
       </c>
       <c r="H37">
         <v>50362</v>
@@ -3687,22 +3784,22 @@
         <v>155</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38">
-        <v>44754</v>
+        <v>101</v>
+      </c>
+      <c r="G38" s="2">
+        <v>44902</v>
       </c>
       <c r="H38">
         <v>48448</v>
@@ -3767,22 +3864,22 @@
         <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G39" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="H39">
         <v>104979</v>
@@ -3847,22 +3944,22 @@
         <v>157</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
-      </c>
-      <c r="G40">
-        <v>43738</v>
+        <v>102</v>
+      </c>
+      <c r="G40" t="s">
+        <v>124</v>
       </c>
       <c r="H40">
         <v>79735</v>
@@ -3927,22 +4024,22 @@
         <v>158</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
-      </c>
-      <c r="G41" t="s">
-        <v>115</v>
+        <v>102</v>
+      </c>
+      <c r="G41" s="2">
+        <v>43475</v>
       </c>
       <c r="H41">
         <v>98893</v>
@@ -4007,22 +4104,22 @@
         <v>159</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G42" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="H42">
         <v>175243</v>
@@ -4087,22 +4184,22 @@
         <v>160</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>102</v>
-      </c>
-      <c r="G43">
-        <v>45573</v>
+        <v>103</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45514</v>
       </c>
       <c r="H43">
         <v>4504</v>
@@ -4167,22 +4264,22 @@
         <v>161</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>102</v>
-      </c>
-      <c r="G44">
-        <v>45768</v>
+        <v>103</v>
+      </c>
+      <c r="G44" t="s">
+        <v>133</v>
       </c>
       <c r="H44">
         <v>1369</v>
@@ -4247,22 +4344,22 @@
         <v>162</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="H45">
         <v>51184</v>
@@ -4327,22 +4424,22 @@
         <v>163</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G46">
-        <v>45510</v>
+        <v>105</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45451</v>
       </c>
       <c r="H46">
         <v>17717</v>
@@ -4407,22 +4504,22 @@
         <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47">
-        <v>45510</v>
+        <v>105</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45451</v>
       </c>
       <c r="H47">
         <v>21106</v>
@@ -4487,22 +4584,22 @@
         <v>165</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
-        <v>105</v>
-      </c>
-      <c r="G48">
-        <v>44855</v>
+        <v>106</v>
+      </c>
+      <c r="G48" t="s">
+        <v>123</v>
       </c>
       <c r="H48">
         <v>38204</v>
@@ -4567,22 +4664,22 @@
         <v>166</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F49" t="s">
-        <v>105</v>
-      </c>
-      <c r="G49">
-        <v>44855</v>
+        <v>106</v>
+      </c>
+      <c r="G49" t="s">
+        <v>123</v>
       </c>
       <c r="H49">
         <v>37973</v>
@@ -4647,22 +4744,22 @@
         <v>167</v>
       </c>
       <c r="B50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D50">
         <v>2025</v>
       </c>
       <c r="E50" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F50" t="s">
-        <v>106</v>
-      </c>
-      <c r="G50">
-        <v>44991</v>
+        <v>107</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45080</v>
       </c>
       <c r="H50">
         <v>77020</v>
@@ -4727,22 +4824,22 @@
         <v>168</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D51">
         <v>2025</v>
       </c>
       <c r="E51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
-      </c>
-      <c r="G51">
-        <v>44991</v>
+        <v>107</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45080</v>
       </c>
       <c r="H51">
         <v>63857</v>
@@ -4807,22 +4904,22 @@
         <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D52">
         <v>2025</v>
       </c>
       <c r="E52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F52" t="s">
-        <v>106</v>
-      </c>
-      <c r="G52">
-        <v>45625</v>
+        <v>107</v>
+      </c>
+      <c r="G52" t="s">
+        <v>135</v>
       </c>
       <c r="H52">
         <v>32781</v>
@@ -4887,22 +4984,22 @@
         <v>170</v>
       </c>
       <c r="B53" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D53">
         <v>2025</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F53" t="s">
-        <v>106</v>
-      </c>
-      <c r="G53">
-        <v>44868</v>
+        <v>107</v>
+      </c>
+      <c r="G53" s="2">
+        <v>44631</v>
       </c>
       <c r="H53">
         <v>72331</v>
@@ -4967,22 +5064,22 @@
         <v>171</v>
       </c>
       <c r="B54" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D54">
         <v>2025</v>
       </c>
       <c r="E54" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>106</v>
-      </c>
-      <c r="G54">
-        <v>45664</v>
+        <v>107</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45839</v>
       </c>
       <c r="H54">
         <v>16471</v>
@@ -5047,22 +5144,22 @@
         <v>172</v>
       </c>
       <c r="B55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55">
         <v>2025</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
-      </c>
-      <c r="G55">
-        <v>45804</v>
+        <v>107</v>
+      </c>
+      <c r="G55" t="s">
+        <v>136</v>
       </c>
       <c r="H55">
         <v>108</v>
@@ -5127,22 +5224,22 @@
         <v>173</v>
       </c>
       <c r="B56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56">
         <v>2025</v>
       </c>
       <c r="E56" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F56" t="s">
-        <v>107</v>
-      </c>
-      <c r="G56">
-        <v>44972</v>
+        <v>108</v>
+      </c>
+      <c r="G56" t="s">
+        <v>137</v>
       </c>
       <c r="H56">
         <v>67357</v>
@@ -5207,22 +5304,22 @@
         <v>174</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57">
         <v>2025</v>
       </c>
       <c r="E57" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F57" t="s">
-        <v>108</v>
-      </c>
-      <c r="G57">
-        <v>44712</v>
+        <v>109</v>
+      </c>
+      <c r="G57" t="s">
+        <v>138</v>
       </c>
       <c r="H57">
         <v>36616</v>
@@ -5287,22 +5384,22 @@
         <v>175</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58">
         <v>2025</v>
       </c>
       <c r="E58" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F58" t="s">
-        <v>108</v>
-      </c>
-      <c r="G58">
-        <v>44719</v>
+        <v>109</v>
+      </c>
+      <c r="G58" s="2">
+        <v>44748</v>
       </c>
       <c r="H58">
         <v>30987</v>
@@ -5367,21 +5464,21 @@
         <v>176</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59">
         <v>2025</v>
       </c>
       <c r="E59" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F59" t="s">
-        <v>108</v>
-      </c>
-      <c r="G59">
+        <v>109</v>
+      </c>
+      <c r="G59" s="2">
         <v>44686</v>
       </c>
       <c r="H59">
@@ -5447,22 +5544,22 @@
         <v>177</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D60">
         <v>2025</v>
       </c>
       <c r="E60" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F60" t="s">
-        <v>109</v>
-      </c>
-      <c r="G60">
-        <v>45520</v>
+        <v>110</v>
+      </c>
+      <c r="G60" t="s">
+        <v>139</v>
       </c>
       <c r="H60">
         <v>19049</v>
@@ -5527,22 +5624,22 @@
         <v>178</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61">
         <v>2025</v>
       </c>
       <c r="E61" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F61" t="s">
-        <v>109</v>
-      </c>
-      <c r="G61">
-        <v>45520</v>
+        <v>110</v>
+      </c>
+      <c r="G61" t="s">
+        <v>139</v>
       </c>
       <c r="H61">
         <v>25141</v>
@@ -5607,22 +5704,22 @@
         <v>179</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D62">
         <v>2025</v>
       </c>
       <c r="E62" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F62" t="s">
-        <v>109</v>
-      </c>
-      <c r="G62">
-        <v>45520</v>
+        <v>110</v>
+      </c>
+      <c r="G62" t="s">
+        <v>139</v>
       </c>
       <c r="H62">
         <v>42913</v>
@@ -5687,22 +5784,22 @@
         <v>180</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D63">
         <v>2025</v>
       </c>
       <c r="E63" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F63" t="s">
-        <v>110</v>
-      </c>
-      <c r="G63">
-        <v>44987</v>
+        <v>111</v>
+      </c>
+      <c r="G63" s="2">
+        <v>44960</v>
       </c>
       <c r="H63">
         <v>95577</v>
@@ -5767,22 +5864,22 @@
         <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D64">
         <v>2025</v>
       </c>
       <c r="E64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F64" t="s">
-        <v>110</v>
-      </c>
-      <c r="G64">
-        <v>45279</v>
+        <v>111</v>
+      </c>
+      <c r="G64" t="s">
+        <v>140</v>
       </c>
       <c r="H64">
         <v>47448</v>
@@ -5847,22 +5944,22 @@
         <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>2025</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F65" t="s">
-        <v>110</v>
-      </c>
-      <c r="G65">
-        <v>45835</v>
+        <v>111</v>
+      </c>
+      <c r="G65" t="s">
+        <v>141</v>
       </c>
       <c r="H65">
         <v>85</v>
@@ -5927,22 +6024,22 @@
         <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D66">
         <v>2025</v>
       </c>
       <c r="E66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F66" t="s">
-        <v>111</v>
-      </c>
-      <c r="G66">
-        <v>45769</v>
+        <v>112</v>
+      </c>
+      <c r="G66" t="s">
+        <v>142</v>
       </c>
       <c r="H66">
         <v>879</v>
@@ -6007,22 +6104,22 @@
         <v>184</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D67">
         <v>2025</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F67" t="s">
-        <v>112</v>
-      </c>
-      <c r="G67">
-        <v>43908</v>
+        <v>113</v>
+      </c>
+      <c r="G67" t="s">
+        <v>143</v>
       </c>
       <c r="H67">
         <v>49763</v>
@@ -6087,22 +6184,22 @@
         <v>185</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D68">
         <v>2025</v>
       </c>
       <c r="E68" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F68" t="s">
-        <v>113</v>
-      </c>
-      <c r="G68">
-        <v>45649</v>
+        <v>114</v>
+      </c>
+      <c r="G68" t="s">
+        <v>144</v>
       </c>
       <c r="H68">
         <v>18707</v>
@@ -6167,22 +6264,22 @@
         <v>186</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D69">
         <v>2025</v>
       </c>
       <c r="E69" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F69" t="s">
-        <v>113</v>
-      </c>
-      <c r="G69">
-        <v>45649</v>
+        <v>114</v>
+      </c>
+      <c r="G69" t="s">
+        <v>144</v>
       </c>
       <c r="H69">
         <v>34107</v>
@@ -6247,22 +6344,22 @@
         <v>187</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D70">
         <v>2025</v>
       </c>
       <c r="E70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F70" t="s">
-        <v>113</v>
-      </c>
-      <c r="G70">
-        <v>45649</v>
+        <v>114</v>
+      </c>
+      <c r="G70" t="s">
+        <v>144</v>
       </c>
       <c r="H70">
         <v>20531</v>
@@ -6327,22 +6424,22 @@
         <v>188</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71">
         <v>2025</v>
       </c>
       <c r="E71" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F71" t="s">
-        <v>113</v>
-      </c>
-      <c r="G71">
-        <v>45679</v>
+        <v>114</v>
+      </c>
+      <c r="G71" t="s">
+        <v>145</v>
       </c>
       <c r="H71">
         <v>6720</v>
@@ -6407,22 +6504,22 @@
         <v>189</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C72" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D72">
         <v>2025</v>
       </c>
       <c r="E72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F72" t="s">
-        <v>114</v>
-      </c>
-      <c r="G72">
-        <v>45625</v>
+        <v>115</v>
+      </c>
+      <c r="G72" t="s">
+        <v>135</v>
       </c>
       <c r="H72">
         <v>6890</v>
@@ -6487,22 +6584,22 @@
         <v>190</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D73">
         <v>2025</v>
       </c>
       <c r="E73" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F73" t="s">
-        <v>114</v>
-      </c>
-      <c r="G73">
-        <v>45625</v>
+        <v>115</v>
+      </c>
+      <c r="G73" t="s">
+        <v>135</v>
       </c>
       <c r="H73">
         <v>14507</v>
